--- a/templates/04_nutricao/08_tabela_substituicoes.xlsx
+++ b/templates/04_nutricao/08_tabela_substituicoes.xlsx
@@ -4,22 +4,112 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Tabela_Substituicoes" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Substituições" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Medida</t>
-  </si>
-  <si>
-    <t>Observação</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Alimento Base (100g)</t>
+  </si>
+  <si>
+    <t>Substituição 1</t>
+  </si>
+  <si>
+    <t>Substituição 2</t>
+  </si>
+  <si>
+    <t>Calorias Médias</t>
+  </si>
+  <si>
+    <t>Carboidratos</t>
+  </si>
+  <si>
+    <t>Arroz Integral</t>
+  </si>
+  <si>
+    <t>Batata Doce</t>
+  </si>
+  <si>
+    <t>Mandioquinha</t>
+  </si>
+  <si>
+    <t>130 kcal</t>
+  </si>
+  <si>
+    <t>Pão Integral (2 fatias)</t>
+  </si>
+  <si>
+    <t>Tapioca (2 colheres)</t>
+  </si>
+  <si>
+    <t>Aveia (3 colheres)</t>
+  </si>
+  <si>
+    <t>160 kcal</t>
+  </si>
+  <si>
+    <t>Proteínas</t>
+  </si>
+  <si>
+    <t>Peito de Frango</t>
+  </si>
+  <si>
+    <t>Patinho Moído</t>
+  </si>
+  <si>
+    <t>Ovos (2 unid.)</t>
+  </si>
+  <si>
+    <t>150-180 kcal</t>
+  </si>
+  <si>
+    <t>Tilápia</t>
+  </si>
+  <si>
+    <t>Lombo Suíno</t>
+  </si>
+  <si>
+    <t>Queijo Cottage</t>
+  </si>
+  <si>
+    <t>120-200 kcal</t>
+  </si>
+  <si>
+    <t>Gorduras</t>
+  </si>
+  <si>
+    <t>Azeite de Oliva (1 colh)</t>
+  </si>
+  <si>
+    <t>Castanha do Pará (2 unid)</t>
+  </si>
+  <si>
+    <t>Abacate (2 colh)</t>
+  </si>
+  <si>
+    <t>90 kcal</t>
+  </si>
+  <si>
+    <t>Fibras</t>
+  </si>
+  <si>
+    <t>Brócolis</t>
+  </si>
+  <si>
+    <t>Couve-Flor</t>
+  </si>
+  <si>
+    <t>Vagem</t>
+  </si>
+  <si>
+    <t>30-40 kcal</t>
   </si>
 </sst>
 </file>
@@ -37,7 +127,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -67,9 +156,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,10 +496,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="5" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -421,6 +511,114 @@
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
